--- a/july 2026/LMT_JULY_26/July Orders/Rainbow 17-07-26/Rainbow Cash & carry Barki Road - 20-07-26.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/Rainbow 17-07-26/Rainbow Cash & carry Barki Road - 20-07-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE37EEB4-A0F4-4E57-9490-06A8E3A433C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CD0A81-3F69-46AD-A9A0-1C781F2DBAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3379,7 +3379,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3407,7 +3407,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4622,7 +4622,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4650,7 +4650,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5865,7 +5865,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5893,7 +5893,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7108,7 +7108,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7136,7 +7136,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8351,7 +8351,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8379,7 +8379,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9594,7 +9594,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9622,7 +9622,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10837,7 +10837,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10865,7 +10865,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12080,7 +12080,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12108,7 +12108,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13323,7 +13323,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13351,7 +13351,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14566,7 +14566,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14594,7 +14594,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18559,7 +18559,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18587,7 +18587,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19799,7 +19799,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19827,7 +19827,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21038,7 +21038,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21066,7 +21066,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22277,7 +22277,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22305,7 +22305,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23521,7 +23521,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23549,7 +23549,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25066,7 +25066,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25094,7 +25094,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -26308,7 +26308,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26336,7 +26336,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27551,7 +27551,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27579,7 +27579,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28793,7 +28793,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28821,7 +28821,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30036,7 +30036,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30064,7 +30064,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31280,7 +31280,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31308,7 +31308,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46222</v>
+        <v>46223</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>

--- a/july 2026/LMT_JULY_26/July Orders/Rainbow 17-07-26/Rainbow Cash & carry Barki Road - 20-07-26.xlsx
+++ b/july 2026/LMT_JULY_26/July Orders/Rainbow 17-07-26/Rainbow Cash & carry Barki Road - 20-07-26.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CD0A81-3F69-46AD-A9A0-1C781F2DBAF5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4947FC1E-0DC4-4C8B-A7B7-2804C9E57425}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" tabRatio="949" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3379,7 +3379,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -3407,7 +3407,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -4622,7 +4622,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -4650,7 +4650,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -5865,7 +5865,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -5893,7 +5893,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -7108,7 +7108,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -7136,7 +7136,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -8351,7 +8351,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -8379,7 +8379,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -9594,7 +9594,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -9622,7 +9622,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -10837,7 +10837,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -10865,7 +10865,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -12080,7 +12080,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -12108,7 +12108,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -13323,7 +13323,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -13351,7 +13351,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -14566,7 +14566,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -14594,7 +14594,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -18559,7 +18559,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -18587,7 +18587,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -19799,7 +19799,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -19827,7 +19827,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -21038,7 +21038,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -21066,7 +21066,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -22277,7 +22277,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -22305,7 +22305,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23521,7 +23521,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -23549,7 +23549,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -23760,7 +23760,7 @@
       </c>
       <c r="U14" s="163">
         <f>+'1'!P35</f>
-        <v>14948.135232000001</v>
+        <v>14371.926819480001</v>
       </c>
       <c r="XFD14" t="s">
         <v>75</v>
@@ -23846,11 +23846,11 @@
       <c r="G16" s="113"/>
       <c r="H16" s="171">
         <f>+'1'!H16+'2'!H16+'4'!H16+'3'!H16+'5'!H16+'6'!H16+'7'!H16+'8'!H16+'9'!H16+'10'!H16+'11'!H16+'12'!H16+'13'!H16+'14'!H16+'15'!H16+'16'!H16+'17'!H16+'18'!H16</f>
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="I16" s="1">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
+        <v>-419.7</v>
       </c>
       <c r="J16" s="171">
         <f>+'1'!J16+'2'!J16+'4'!J16+'3'!J16+'5'!J16+'6'!J16+'7'!J16+'8'!J16+'9'!J16+'10'!J16+'11'!J16+'12'!J16+'13'!J16+'14'!J16+'15'!J16+'16'!J16+'17'!J16+'18'!J16</f>
@@ -23862,23 +23862,23 @@
       </c>
       <c r="L16" s="174">
         <f>+'1'!L16+'2'!L16+'4'!L16+'3'!L16+'5'!L16+'6'!L16+'7'!L16+'8'!L16+'9'!L16+'10'!L16</f>
-        <v>0</v>
+        <v>-58.758000000000003</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>0</v>
+        <v>-360.94200000000001</v>
       </c>
       <c r="N16" s="100">
         <f>+'1'!N16+'2'!N16+'4'!N16+'3'!N16+'5'!N16+'6'!N16+'7'!N16+'8'!N16+'9'!N16+'10'!N16</f>
-        <v>0</v>
+        <v>-64.969560000000001</v>
       </c>
       <c r="O16" s="100">
         <f>+'1'!O16+'2'!O16+'4'!O16+'3'!O16+'5'!O16+'6'!O16+'7'!O16+'8'!O16+'9'!O16+'10'!O16</f>
-        <v>0</v>
+        <v>-2.1295578000000002</v>
       </c>
       <c r="P16" s="104">
         <f t="shared" ref="P16:P24" si="0">M16+N16+O16</f>
-        <v>0</v>
+        <v>-428.04111779999999</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="T16" s="162" t="str">
@@ -24064,11 +24064,11 @@
       <c r="G19" s="113"/>
       <c r="H19" s="171">
         <f>+'1'!H19+'2'!H19+'4'!H19+'3'!H19+'5'!H19+'6'!H19+'7'!H19+'8'!H19+'9'!H19+'10'!H19+'11'!H19+'12'!H19+'13'!H19+'14'!H19+'15'!H19+'16'!H19+'17'!H19+'18'!H19</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I19" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-72.64</v>
       </c>
       <c r="J19" s="171">
         <f>+'1'!J19+'2'!J19+'4'!J19+'3'!J19+'5'!J19+'6'!J19+'7'!J19+'8'!J19+'9'!J19+'10'!J19+'11'!J19+'12'!J19+'13'!J19+'14'!J19+'15'!J19+'16'!J19+'17'!J19+'18'!J19</f>
@@ -24080,23 +24080,23 @@
       </c>
       <c r="L19" s="174">
         <f>+'1'!L19+'2'!L19+'4'!L19+'3'!L19+'5'!L19+'6'!L19+'7'!L19+'8'!L19+'9'!L19+'10'!L19</f>
-        <v>0</v>
+        <v>-10.169600000000001</v>
       </c>
       <c r="M19" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-62.470399999999998</v>
       </c>
       <c r="N19" s="100">
         <f>+'1'!N19+'2'!N19+'4'!N19+'3'!N19+'5'!N19+'6'!N19+'7'!N19+'8'!N19+'9'!N19+'10'!N19</f>
-        <v>0</v>
+        <v>-11.244672</v>
       </c>
       <c r="O19" s="100">
         <f>+'1'!O19+'2'!O19+'4'!O19+'3'!O19+'5'!O19+'6'!O19+'7'!O19+'8'!O19+'9'!O19+'10'!O19</f>
-        <v>0</v>
+        <v>-0.36857535999999996</v>
       </c>
       <c r="P19" s="119">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-74.083647359999986</v>
       </c>
       <c r="T19" s="162" t="str">
         <f>+'6'!A5</f>
@@ -24134,11 +24134,11 @@
       <c r="G20" s="113"/>
       <c r="H20" s="171">
         <f>+'1'!H20+'2'!H20+'4'!H20+'3'!H20+'5'!H20+'6'!H20+'7'!H20+'8'!H20+'9'!H20+'10'!H20+'11'!H20+'12'!H20+'13'!H20+'14'!H20+'15'!H20+'16'!H20+'17'!H20+'18'!H20</f>
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I20" s="1">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>-72.64</v>
       </c>
       <c r="J20" s="171">
         <f>+'1'!J20+'2'!J20+'4'!J20+'3'!J20+'5'!J20+'6'!J20+'7'!J20+'8'!J20+'9'!J20+'10'!J20+'11'!J20+'12'!J20+'13'!J20+'14'!J20+'15'!J20+'16'!J20+'17'!J20+'18'!J20</f>
@@ -24150,23 +24150,23 @@
       </c>
       <c r="L20" s="174">
         <f>+'1'!L20+'2'!L20+'4'!L20+'3'!L20+'5'!L20+'6'!L20+'7'!L20+'8'!L20+'9'!L20+'10'!L20</f>
-        <v>0</v>
+        <v>-10.169600000000001</v>
       </c>
       <c r="M20" s="117">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-62.470399999999998</v>
       </c>
       <c r="N20" s="100">
         <f>+'1'!N20+'2'!N20+'4'!N20+'3'!N20+'5'!N20+'6'!N20+'7'!N20+'8'!N20+'9'!N20+'10'!N20</f>
-        <v>0</v>
+        <v>-11.244672</v>
       </c>
       <c r="O20" s="100">
         <f>+'1'!O20+'2'!O20+'4'!O20+'3'!O20+'5'!O20+'6'!O20+'7'!O20+'8'!O20+'9'!O20+'10'!O20</f>
-        <v>0</v>
+        <v>-0.36857535999999996</v>
       </c>
       <c r="P20" s="119">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>-74.083647359999986</v>
       </c>
       <c r="T20" s="162" t="str">
         <f>+'7'!A5</f>
@@ -24464,7 +24464,7 @@
       <c r="B25" s="211"/>
       <c r="C25" s="212">
         <f>H25/40</f>
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="D25" s="206"/>
       <c r="E25" s="206"/>
@@ -24475,11 +24475,11 @@
       </c>
       <c r="H25" s="176">
         <f t="shared" si="3"/>
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I25" s="177">
         <f t="shared" si="3"/>
-        <v>14528</v>
+        <v>13963.02</v>
       </c>
       <c r="J25" s="176">
         <f t="shared" si="3"/>
@@ -24491,23 +24491,23 @@
       </c>
       <c r="L25" s="178">
         <f t="shared" si="3"/>
-        <v>2033.9200000000003</v>
+        <v>1954.8228000000004</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="3"/>
-        <v>12494.08</v>
+        <v>12008.197200000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2379.6864</v>
+        <v>2292.227496</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>74.368831999999998</v>
+        <v>71.502123479999995</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14948.135232000001</v>
+        <v>14371.926819480001</v>
       </c>
       <c r="T25" s="162" t="str">
         <f>+'12'!A5</f>
@@ -24715,7 +24715,7 @@
       </c>
       <c r="U33" s="164">
         <f>SUM(U14:U28)</f>
-        <v>14948.135232000001</v>
+        <v>14371.926819480001</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24748,7 +24748,7 @@
       <c r="O35" s="223"/>
       <c r="P35" s="151">
         <f>I25</f>
-        <v>14528</v>
+        <v>13963.02</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24769,7 +24769,7 @@
       <c r="O36" s="225"/>
       <c r="P36" s="152">
         <f>L25</f>
-        <v>2033.9200000000003</v>
+        <v>1954.8228000000004</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24812,7 +24812,7 @@
       <c r="O38" s="225"/>
       <c r="P38" s="152">
         <f>P35-P36-P37</f>
-        <v>12494.08</v>
+        <v>12008.197200000001</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24837,7 +24837,7 @@
       </c>
       <c r="P39" s="152">
         <f>N25</f>
-        <v>2379.6864</v>
+        <v>2292.227496</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -24859,7 +24859,7 @@
       <c r="O40" s="227"/>
       <c r="P40" s="152">
         <f>P38+P39</f>
-        <v>14873.7664</v>
+        <v>14300.424696</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24884,7 +24884,7 @@
       </c>
       <c r="P41" s="152">
         <f>O41*P40</f>
-        <v>371.84416000000004</v>
+        <v>357.5106174</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -24894,7 +24894,7 @@
       <c r="O42" s="205"/>
       <c r="P42" s="159">
         <f>P40+P41</f>
-        <v>15245.610560000001</v>
+        <v>14657.935313399999</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -24995,7 +24995,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:XFD37"/>
+  <dimension ref="A2:XFD38"/>
   <sheetFormatPr defaultColWidth="29.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" customWidth="1"/>
@@ -25065,8 +25065,7 @@
       <c r="L4" s="230"/>
       <c r="M4" s="230"/>
       <c r="N4" s="244">
-        <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -25093,8 +25092,8 @@
       <c r="L5" s="230"/>
       <c r="M5" s="230"/>
       <c r="N5" s="244">
-        <f ca="1">N4-1</f>
-        <v>46223</v>
+        <f>N4-1</f>
+        <v>46225</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -25386,38 +25385,37 @@
         <v>52.462499999999999</v>
       </c>
       <c r="G16" s="99"/>
-      <c r="H16" s="100"/>
+      <c r="H16" s="100">
+        <v>-8</v>
+      </c>
       <c r="I16" s="101">
         <f>(G16*D16)*F16+H16*F16</f>
-        <v>0</v>
-      </c>
-      <c r="J16" s="102">
-        <f>H16/20</f>
-        <v>0</v>
-      </c>
-      <c r="K16" s="103">
-        <f>I16*3.5%</f>
+        <v>-419.7</v>
+      </c>
+      <c r="J16" s="102"/>
+      <c r="K16" s="1">
+        <f t="shared" ref="K16:K21" si="0">I16*$K$13</f>
         <v>0</v>
       </c>
       <c r="L16" s="104">
         <f>I16*14%</f>
-        <v>0</v>
+        <v>-58.758000000000003</v>
       </c>
       <c r="M16" s="105">
         <f>I16-K16-L16</f>
-        <v>0</v>
+        <v>-360.94200000000001</v>
       </c>
       <c r="N16" s="105">
-        <f t="shared" ref="N16:N24" si="0">(M16*$N$15)+(J16*F16)*$N$15</f>
-        <v>0</v>
+        <f t="shared" ref="N16:N24" si="1">(M16*$N$15)+(J16*F16)*$N$15</f>
+        <v>-64.969560000000001</v>
       </c>
       <c r="O16" s="106">
-        <f t="shared" ref="O16:O24" si="1">(N16+M16)*$O$15</f>
-        <v>0</v>
+        <f t="shared" ref="O16:O24" si="2">(N16+M16)*$O$15</f>
+        <v>-2.1295578000000002</v>
       </c>
       <c r="P16" s="104">
-        <f t="shared" ref="P16:P24" si="2">M16+N16+O16</f>
-        <v>0</v>
+        <f t="shared" ref="P16:P24" si="3">M16+N16+O16</f>
+        <v>-428.04111779999999</v>
       </c>
       <c r="Q16" s="107"/>
       <c r="XFD16" t="s">
@@ -25451,35 +25449,32 @@
       <c r="G17" s="113"/>
       <c r="H17" s="114"/>
       <c r="I17" s="115">
-        <f t="shared" ref="I17:I23" si="3">(G17*D17)*F17+H17*F17</f>
-        <v>0</v>
-      </c>
-      <c r="J17" s="102">
-        <f t="shared" ref="J17:J21" si="4">H17/20</f>
-        <v>0</v>
-      </c>
+        <f t="shared" ref="I17:I23" si="4">(G17*D17)*F17+H17*F17</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="102"/>
       <c r="K17" s="1">
-        <f t="shared" ref="K17:K21" si="5">I17*$K$13</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L17" s="104">
-        <f t="shared" ref="L17:L21" si="6">I17*14%</f>
+        <f t="shared" ref="L17:L22" si="5">I17*14%</f>
         <v>0</v>
       </c>
       <c r="M17" s="117">
-        <f t="shared" ref="M17:M23" si="7">I17-K17-L17</f>
+        <f t="shared" ref="M17:M23" si="6">I17-K17-L17</f>
         <v>0</v>
       </c>
       <c r="N17" s="117">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O17" s="118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P17" s="119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="S17" s="64"/>
@@ -25514,35 +25509,32 @@
       <c r="G18" s="113"/>
       <c r="H18" s="114"/>
       <c r="I18" s="115">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="J18" s="102"/>
+      <c r="K18" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L18" s="104">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="M18" s="117">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="N18" s="117">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="O18" s="118">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="P18" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J18" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L18" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M18" s="117">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N18" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O18" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="119">
-        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -25571,38 +25563,37 @@
         <v>72.64</v>
       </c>
       <c r="G19" s="113"/>
-      <c r="H19" s="114"/>
+      <c r="H19" s="114">
+        <v>-1</v>
+      </c>
       <c r="I19" s="115">
+        <f t="shared" si="4"/>
+        <v>-72.64</v>
+      </c>
+      <c r="J19" s="102"/>
+      <c r="K19" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L19" s="104">
+        <f t="shared" si="5"/>
+        <v>-10.169600000000001</v>
+      </c>
+      <c r="M19" s="117">
+        <f t="shared" si="6"/>
+        <v>-62.470399999999998</v>
+      </c>
+      <c r="N19" s="117">
+        <f t="shared" si="1"/>
+        <v>-11.244672</v>
+      </c>
+      <c r="O19" s="118">
+        <f t="shared" si="2"/>
+        <v>-0.36857535999999996</v>
+      </c>
+      <c r="P19" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J19" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L19" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M19" s="117">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O19" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P19" s="119">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-74.083647359999986</v>
       </c>
     </row>
     <row r="20" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25630,38 +25621,37 @@
         <v>72.64</v>
       </c>
       <c r="G20" s="113"/>
-      <c r="H20" s="114"/>
+      <c r="H20" s="114">
+        <v>-1</v>
+      </c>
       <c r="I20" s="115">
+        <f t="shared" si="4"/>
+        <v>-72.64</v>
+      </c>
+      <c r="J20" s="102"/>
+      <c r="K20" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L20" s="104">
+        <f t="shared" si="5"/>
+        <v>-10.169600000000001</v>
+      </c>
+      <c r="M20" s="117">
+        <f t="shared" si="6"/>
+        <v>-62.470399999999998</v>
+      </c>
+      <c r="N20" s="117">
+        <f t="shared" si="1"/>
+        <v>-11.244672</v>
+      </c>
+      <c r="O20" s="118">
+        <f t="shared" si="2"/>
+        <v>-0.36857535999999996</v>
+      </c>
+      <c r="P20" s="119">
         <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="J20" s="102">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L20" s="104">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="M20" s="117">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="N20" s="117">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="O20" s="118">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P20" s="119">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <v>-74.083647359999986</v>
       </c>
     </row>
     <row r="21" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25693,35 +25683,35 @@
         <v>200</v>
       </c>
       <c r="I21" s="115">
+        <f t="shared" si="4"/>
+        <v>14528</v>
+      </c>
+      <c r="J21" s="102">
+        <f t="shared" ref="J17:J21" si="7">H21/20</f>
+        <v>10</v>
+      </c>
+      <c r="K21" s="1">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="L21" s="104">
+        <f>I21*14%</f>
+        <v>2033.9200000000003</v>
+      </c>
+      <c r="M21" s="117">
+        <f t="shared" si="6"/>
+        <v>12494.08</v>
+      </c>
+      <c r="N21" s="117">
+        <f t="shared" si="1"/>
+        <v>2379.6864</v>
+      </c>
+      <c r="O21" s="118">
+        <f t="shared" si="2"/>
+        <v>74.368831999999998</v>
+      </c>
+      <c r="P21" s="119">
         <f t="shared" si="3"/>
-        <v>14528</v>
-      </c>
-      <c r="J21" s="102">
-        <f t="shared" si="4"/>
-        <v>10</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="L21" s="104">
-        <f t="shared" si="6"/>
-        <v>2033.9200000000003</v>
-      </c>
-      <c r="M21" s="117">
-        <f t="shared" si="7"/>
-        <v>12494.08</v>
-      </c>
-      <c r="N21" s="117">
-        <f t="shared" si="0"/>
-        <v>2379.6864</v>
-      </c>
-      <c r="O21" s="118">
-        <f t="shared" si="1"/>
-        <v>74.368831999999998</v>
-      </c>
-      <c r="P21" s="119">
-        <f t="shared" si="2"/>
         <v>14948.135232000001</v>
       </c>
     </row>
@@ -25752,7 +25742,7 @@
       <c r="G22" s="113"/>
       <c r="H22" s="114"/>
       <c r="I22" s="115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J22" s="116"/>
@@ -25760,24 +25750,24 @@
         <f>I22*3.5%</f>
         <v>0</v>
       </c>
-      <c r="L22" s="119">
-        <f>I22*5%</f>
+      <c r="L22" s="104">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="M22" s="117">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N22" s="117">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O22" s="118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P22" s="119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -25808,7 +25798,7 @@
       <c r="G23" s="113"/>
       <c r="H23" s="114"/>
       <c r="I23" s="115">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="J23" s="116"/>
@@ -25821,19 +25811,19 @@
         <v>0</v>
       </c>
       <c r="M23" s="117">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="N23" s="117">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O23" s="118">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P23" s="119">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -25881,15 +25871,15 @@
         <v>0</v>
       </c>
       <c r="N24" s="132">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="O24" s="133">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="P24" s="131">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -25908,11 +25898,11 @@
       </c>
       <c r="H25" s="135">
         <f t="shared" si="10"/>
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="I25" s="136">
         <f t="shared" si="10"/>
-        <v>14528</v>
+        <v>13963.02</v>
       </c>
       <c r="J25" s="182">
         <f>SUM(J16:J21)</f>
@@ -25924,23 +25914,23 @@
       </c>
       <c r="L25" s="139">
         <f t="shared" si="10"/>
-        <v>2033.9200000000003</v>
+        <v>1954.8228000000004</v>
       </c>
       <c r="M25" s="140">
         <f t="shared" si="10"/>
-        <v>12494.08</v>
+        <v>12008.197200000001</v>
       </c>
       <c r="N25" s="141">
         <f>SUM(N16:N24)</f>
-        <v>2379.6864</v>
+        <v>2292.227496</v>
       </c>
       <c r="O25" s="142">
         <f>SUM(O16:O24)</f>
-        <v>74.368831999999998</v>
+        <v>71.502123479999995</v>
       </c>
       <c r="P25" s="143">
         <f>SUM(P16:P24)</f>
-        <v>14948.135232000001</v>
+        <v>14371.926819480001</v>
       </c>
     </row>
     <row r="26" spans="1:19 16384:16384" x14ac:dyDescent="0.35">
@@ -25990,7 +25980,7 @@
       <c r="O28" s="223"/>
       <c r="P28" s="151">
         <f>I25</f>
-        <v>14528</v>
+        <v>13963.02</v>
       </c>
     </row>
     <row r="29" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26011,7 +26001,7 @@
       <c r="O29" s="225"/>
       <c r="P29" s="152">
         <f>L25</f>
-        <v>2033.9200000000003</v>
+        <v>1954.8228000000004</v>
       </c>
     </row>
     <row r="30" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26054,7 +26044,7 @@
       <c r="O31" s="225"/>
       <c r="P31" s="152">
         <f>P28-P29-P30</f>
-        <v>12494.08</v>
+        <v>12008.197200000001</v>
       </c>
     </row>
     <row r="32" spans="1:19 16384:16384" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26079,7 +26069,7 @@
       </c>
       <c r="P32" s="152">
         <f>N25</f>
-        <v>2379.6864</v>
+        <v>2292.227496</v>
       </c>
     </row>
     <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
@@ -26101,7 +26091,7 @@
       <c r="O33" s="227"/>
       <c r="P33" s="152">
         <f>P31+P32</f>
-        <v>14873.7664</v>
+        <v>14300.424696</v>
       </c>
     </row>
     <row r="34" spans="2:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26126,7 +26116,7 @@
       </c>
       <c r="P34" s="152">
         <f>O34*P33</f>
-        <v>74.368831999999998</v>
+        <v>71.502123480000009</v>
       </c>
     </row>
     <row r="35" spans="2:16" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
@@ -26136,7 +26126,7 @@
       <c r="O35" s="205"/>
       <c r="P35" s="159">
         <f>P33+P34</f>
-        <v>14948.135232000001</v>
+        <v>14371.926819480001</v>
       </c>
     </row>
     <row r="36" spans="2:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -26153,7 +26143,12 @@
       <c r="J36" s="208"/>
       <c r="K36" s="209"/>
     </row>
-    <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="37" spans="2:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P37" s="64"/>
+    </row>
+    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+      <c r="N38" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="47">
     <mergeCell ref="A2:C2"/>
@@ -26308,7 +26303,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -26336,7 +26331,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -27551,7 +27546,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -27579,7 +27574,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -28793,7 +28788,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -28821,7 +28816,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -30036,7 +30031,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -30064,7 +30059,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
@@ -31280,7 +31275,7 @@
       <c r="M4" s="230"/>
       <c r="N4" s="244">
         <f ca="1">TODAY()</f>
-        <v>46224</v>
+        <v>46227</v>
       </c>
       <c r="O4" s="244"/>
       <c r="P4" s="244"/>
@@ -31308,7 +31303,7 @@
       <c r="M5" s="230"/>
       <c r="N5" s="244">
         <f ca="1">N4-1</f>
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="O5" s="231"/>
       <c r="P5" s="231"/>
